--- a/dev_docs/Tetra数值公式_26_4_21.xlsx
+++ b/dev_docs/Tetra数值公式_26_4_21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD1EF48-D664-4F44-BDA3-9FA56DA0C42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC80A17-5747-4271-A82E-01B0EC68A2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="366">
   <si>
     <t>刀刃</t>
   </si>
@@ -1240,10 +1240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>击退抗性+0.</t>
     </r>
@@ -1285,10 +1281,6 @@
     <t>'cataclysm:ancient_metal_ingot'</t>
   </si>
   <si>
-    <t>!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>远古金属</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1413,6 +1405,50 @@
   </si>
   <si>
     <t>冰霜伤害+14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/manasteel'</t>
+  </si>
+  <si>
+    <t>魔力钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力修复3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力共振1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力共振：特殊词条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他特性4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法穿透+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1590,7 +1626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1670,6 +1706,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1947,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X161"/>
+  <dimension ref="A1:X162"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
@@ -1995,6 +2037,9 @@
       <c r="S1" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="T1" s="24" t="s">
+        <v>362</v>
+      </c>
       <c r="U1" s="27" t="s">
         <v>294</v>
       </c>
@@ -2045,6 +2090,9 @@
       <c r="S2" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="T2" s="29" t="s">
+        <v>363</v>
+      </c>
       <c r="U2" s="27" t="s">
         <v>303</v>
       </c>
@@ -2317,6 +2365,9 @@
       <c r="S10" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="T10" s="30" t="s">
+        <v>364</v>
+      </c>
       <c r="U10" s="3" t="s">
         <v>324</v>
       </c>
@@ -5230,10 +5281,10 @@
         <v>4</v>
       </c>
       <c r="Q62" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="R62" s="23" t="s">
         <v>331</v>
-      </c>
-      <c r="R62" s="23" t="s">
-        <v>332</v>
       </c>
       <c r="S62" s="9"/>
       <c r="U62" s="24"/>
@@ -5779,23 +5830,23 @@
         <v>7</v>
       </c>
       <c r="J72" s="17">
-        <f t="shared" ref="J72:J79" si="37">(G72*$I$2)+(H72*$I$3)</f>
+        <f t="shared" ref="J72:J80" si="37">(G72*$I$2)+(H72*$I$3)</f>
         <v>31</v>
       </c>
       <c r="K72" s="9">
-        <f t="shared" ref="K72:K79" si="38">(G72*$I$5)+(H72*$I$6)+(I72*$I$7)</f>
+        <f t="shared" ref="K72:K80" si="38">(G72*$I$5)+(H72*$I$6)+(I72*$I$7)</f>
         <v>10</v>
       </c>
       <c r="L72" s="10">
-        <f t="shared" ref="L72:L79" si="39">J72+K72</f>
+        <f t="shared" ref="L72:L80" si="39">J72+K72</f>
         <v>41</v>
       </c>
       <c r="M72" s="11">
-        <f t="shared" ref="M72:M79" si="40">I72*$M$2</f>
+        <f t="shared" ref="M72:M80" si="40">I72*$M$2</f>
         <v>43.75</v>
       </c>
       <c r="N72" s="11">
-        <f t="shared" ref="N72:N79" si="41">I72*$M$3</f>
+        <f t="shared" ref="N72:N80" si="41">I72*$M$3</f>
         <v>10.5</v>
       </c>
       <c r="O72" s="9">
@@ -5869,283 +5920,285 @@
       <c r="S73" s="9"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="C74" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="5">
+        <v>14</v>
+      </c>
+      <c r="H74" s="5">
+        <v>5</v>
+      </c>
+      <c r="I74" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="J74" s="17">
+        <f t="shared" ref="J74" si="42">(G74*$I$2)+(H74*$I$3)</f>
+        <v>30.5</v>
+      </c>
+      <c r="K74" s="9">
+        <f t="shared" ref="K74" si="43">(G74*$I$5)+(H74*$I$6)+(I74*$I$7)</f>
+        <v>9.5</v>
+      </c>
+      <c r="L74" s="10">
+        <f t="shared" ref="L74" si="44">J74+K74</f>
+        <v>40</v>
+      </c>
+      <c r="M74" s="11">
+        <f t="shared" ref="M74" si="45">I74*$M$2</f>
+        <v>46.875</v>
+      </c>
+      <c r="N74" s="11">
+        <f t="shared" ref="N74" si="46">I74*$M$3</f>
+        <v>11.25</v>
+      </c>
+      <c r="O74" s="9">
+        <v>6</v>
+      </c>
+      <c r="P74" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q74" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="R74" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="S74" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="U74" s="24"/>
+    </row>
+    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
         <v>45</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B75" s="3">
         <v>50</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C75" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D75" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E75" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F75" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G74" s="12">
+      <c r="G75" s="12">
         <v>15.5</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H75" s="12">
         <v>6</v>
       </c>
-      <c r="I74" s="12">
+      <c r="I75" s="12">
         <v>8</v>
       </c>
-      <c r="J74" s="17">
+      <c r="J75" s="17">
         <f t="shared" si="37"/>
         <v>34</v>
       </c>
-      <c r="K74" s="9">
+      <c r="K75" s="9">
         <f t="shared" si="38"/>
         <v>10.75</v>
       </c>
-      <c r="L74" s="10">
+      <c r="L75" s="10">
         <f t="shared" si="39"/>
         <v>44.75</v>
       </c>
-      <c r="M74" s="11">
+      <c r="M75" s="11">
         <f t="shared" si="40"/>
         <v>50</v>
       </c>
-      <c r="N74" s="11">
+      <c r="N75" s="11">
         <f t="shared" si="41"/>
         <v>12</v>
       </c>
-      <c r="O74" s="9">
+      <c r="O75" s="9">
         <v>6</v>
       </c>
-      <c r="P74" s="9">
+      <c r="P75" s="9">
         <v>6</v>
       </c>
-      <c r="Q74" s="9" t="s">
+      <c r="Q75" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="R74" s="9" t="s">
+      <c r="R75" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="S74" s="9"/>
-    </row>
-    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="12" t="s">
+      <c r="S75" s="9"/>
+    </row>
+    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D76" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E76" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="F76" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G76" s="12">
         <v>13</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H76" s="12">
         <v>5</v>
       </c>
-      <c r="I75" s="12">
+      <c r="I76" s="12">
         <v>7</v>
       </c>
-      <c r="J75" s="17">
+      <c r="J76" s="17">
         <f t="shared" si="37"/>
         <v>28.5</v>
       </c>
-      <c r="K75" s="9">
+      <c r="K76" s="9">
         <f t="shared" si="38"/>
         <v>9</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L76" s="10">
         <f t="shared" si="39"/>
         <v>37.5</v>
       </c>
-      <c r="M75" s="11">
+      <c r="M76" s="11">
         <f t="shared" si="40"/>
         <v>43.75</v>
       </c>
-      <c r="N75" s="11">
+      <c r="N76" s="11">
         <f t="shared" si="41"/>
         <v>10.5</v>
       </c>
-      <c r="O75" s="9">
+      <c r="O76" s="9">
         <v>5</v>
       </c>
-      <c r="P75" s="9">
+      <c r="P76" s="9">
         <v>5</v>
       </c>
-      <c r="Q75" s="23" t="s">
+      <c r="Q76" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="R75" s="23" t="s">
+      <c r="R76" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="S75" s="9"/>
-    </row>
-    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="S76" s="9"/>
+    </row>
+    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
         <v>40</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B77" s="3">
         <v>45</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C77" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G77" s="5">
         <v>14</v>
       </c>
-      <c r="H76" s="5">
+      <c r="H77" s="5">
         <v>5</v>
       </c>
-      <c r="I76" s="5">
+      <c r="I77" s="5">
         <v>7.5</v>
       </c>
-      <c r="J76" s="17">
+      <c r="J77" s="17">
         <f t="shared" si="37"/>
         <v>30.5</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K77" s="9">
         <f t="shared" si="38"/>
         <v>9.5</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L77" s="10">
         <f t="shared" si="39"/>
         <v>40</v>
       </c>
-      <c r="M76" s="11">
+      <c r="M77" s="11">
         <f t="shared" si="40"/>
         <v>46.875</v>
       </c>
-      <c r="N76" s="11">
+      <c r="N77" s="11">
         <f t="shared" si="41"/>
         <v>11.25</v>
       </c>
-      <c r="O76" s="9">
+      <c r="O77" s="9">
         <v>6</v>
       </c>
-      <c r="P76" s="9">
+      <c r="P77" s="9">
         <v>7</v>
       </c>
-      <c r="Q76" s="23" t="s">
+      <c r="Q77" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="R76" s="23" t="s">
+      <c r="R77" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="S76" s="9"/>
-    </row>
-    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G77" s="5">
-        <v>13</v>
-      </c>
-      <c r="H77" s="5">
-        <v>7</v>
-      </c>
-      <c r="I77" s="5">
-        <v>8</v>
-      </c>
-      <c r="J77" s="17">
-        <f t="shared" ref="J77:J78" si="42">(G77*$I$2)+(H77*$I$3)</f>
-        <v>29.5</v>
-      </c>
-      <c r="K77" s="9">
-        <f t="shared" ref="K77:K78" si="43">(G77*$I$5)+(H77*$I$6)+(I77*$I$7)</f>
-        <v>10</v>
-      </c>
-      <c r="L77" s="10">
-        <f t="shared" ref="L77:L78" si="44">J77+K77</f>
-        <v>39.5</v>
-      </c>
-      <c r="M77" s="11">
-        <f t="shared" ref="M77:M78" si="45">I77*$M$2</f>
-        <v>50</v>
-      </c>
-      <c r="N77" s="11">
-        <f t="shared" ref="N77:N78" si="46">I77*$M$3</f>
-        <v>12</v>
-      </c>
-      <c r="O77" s="9">
-        <v>3</v>
-      </c>
-      <c r="P77" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="R77" s="23"/>
       <c r="S77" s="9"/>
-      <c r="U77" s="24" t="s">
-        <v>335</v>
-      </c>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="F78" s="25" t="s">
-        <v>356</v>
+        <v>347</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="G78" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H78" s="5">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I78" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J78" s="17">
-        <f t="shared" si="42"/>
-        <v>27</v>
+        <f t="shared" ref="J78:J79" si="47">(G78*$I$2)+(H78*$I$3)</f>
+        <v>29.5</v>
       </c>
       <c r="K78" s="9">
-        <f t="shared" si="43"/>
-        <v>13.5</v>
+        <f t="shared" ref="K78:K79" si="48">(G78*$I$5)+(H78*$I$6)+(I78*$I$7)</f>
+        <v>10</v>
       </c>
       <c r="L78" s="10">
-        <f t="shared" si="44"/>
-        <v>40.5</v>
+        <f t="shared" ref="L78:L79" si="49">J78+K78</f>
+        <v>39.5</v>
       </c>
       <c r="M78" s="11">
-        <f t="shared" si="45"/>
-        <v>56.25</v>
+        <f t="shared" ref="M78:M79" si="50">I78*$M$2</f>
+        <v>50</v>
       </c>
       <c r="N78" s="11">
-        <f t="shared" si="46"/>
-        <v>13.5</v>
+        <f t="shared" ref="N78:N79" si="51">I78*$M$3</f>
+        <v>12</v>
       </c>
       <c r="O78" s="9">
         <v>3</v>
@@ -6153,129 +6206,126 @@
       <c r="P78" s="9">
         <v>5</v>
       </c>
-      <c r="Q78" s="23" t="s">
-        <v>357</v>
+      <c r="Q78" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="R78" s="23"/>
       <c r="S78" s="9"/>
-      <c r="U78" s="24" t="s">
-        <v>335</v>
-      </c>
+      <c r="U78" s="24"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="C79" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E79" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="G79" s="5">
+        <v>9</v>
+      </c>
+      <c r="H79" s="5">
+        <v>18</v>
+      </c>
+      <c r="I79" s="5">
+        <v>9</v>
+      </c>
+      <c r="J79" s="17">
+        <f t="shared" si="47"/>
+        <v>27</v>
+      </c>
+      <c r="K79" s="9">
+        <f t="shared" si="48"/>
+        <v>13.5</v>
+      </c>
+      <c r="L79" s="10">
+        <f t="shared" si="49"/>
+        <v>40.5</v>
+      </c>
+      <c r="M79" s="11">
+        <f t="shared" si="50"/>
+        <v>56.25</v>
+      </c>
+      <c r="N79" s="11">
+        <f t="shared" si="51"/>
+        <v>13.5</v>
+      </c>
+      <c r="O79" s="9">
+        <v>3</v>
+      </c>
+      <c r="P79" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="R79" s="23"/>
+      <c r="S79" s="9"/>
+      <c r="U79" s="24"/>
+    </row>
+    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
         <v>50</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B80" s="3">
         <v>60</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C80" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D80" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E80" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F80" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="12">
+      <c r="G80" s="12">
         <v>15</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H80" s="12">
         <v>7</v>
       </c>
-      <c r="I79" s="12">
+      <c r="I80" s="12">
         <v>9.5</v>
       </c>
-      <c r="J79" s="17">
+      <c r="J80" s="17">
         <f t="shared" si="37"/>
         <v>33.5</v>
       </c>
-      <c r="K79" s="9">
+      <c r="K80" s="9">
         <f t="shared" si="38"/>
         <v>11</v>
       </c>
-      <c r="L79" s="10">
+      <c r="L80" s="10">
         <f t="shared" si="39"/>
         <v>44.5</v>
       </c>
-      <c r="M79" s="11">
+      <c r="M80" s="11">
         <f t="shared" si="40"/>
         <v>59.375</v>
       </c>
-      <c r="N79" s="11">
+      <c r="N80" s="11">
         <f t="shared" si="41"/>
         <v>14.25</v>
       </c>
-      <c r="O79" s="9">
-        <v>7</v>
-      </c>
-      <c r="P79" s="9">
-        <v>7</v>
-      </c>
-      <c r="Q79" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-    </row>
-    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C80" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G80" s="12">
-        <v>16</v>
-      </c>
-      <c r="H80" s="12">
-        <v>10</v>
-      </c>
-      <c r="I80" s="12">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J80" s="17">
-        <f t="shared" ref="J80:J93" si="47">(G80*$I$2)+(H80*$I$3)</f>
-        <v>37</v>
-      </c>
-      <c r="K80" s="9">
-        <f t="shared" ref="K80:K93" si="48">(G80*$I$5)+(H80*$I$6)+(I80*$I$7)</f>
-        <v>13</v>
-      </c>
-      <c r="L80" s="10">
-        <f t="shared" ref="L80:L93" si="49">J80+K80</f>
-        <v>50</v>
-      </c>
-      <c r="M80" s="11">
-        <f t="shared" ref="M80:M93" si="50">I80*$M$2</f>
-        <v>61.250000000000007</v>
-      </c>
-      <c r="N80" s="11">
-        <f t="shared" ref="N80:N93" si="51">I80*$M$3</f>
-        <v>14.700000000000001</v>
-      </c>
       <c r="O80" s="9">
         <v>7</v>
       </c>
       <c r="P80" s="9">
         <v>7</v>
       </c>
-      <c r="Q80" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="R80" s="23" t="s">
-        <v>300</v>
-      </c>
+      <c r="Q80" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="R80" s="9"/>
       <c r="S80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6283,161 +6333,159 @@
         <v>240</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E81" s="26" t="s">
-        <v>353</v>
+        <v>241</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G81" s="12">
+        <v>16</v>
+      </c>
+      <c r="H81" s="12">
+        <v>10</v>
+      </c>
+      <c r="I81" s="12">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J81" s="17">
+        <f t="shared" ref="J81:J94" si="52">(G81*$I$2)+(H81*$I$3)</f>
+        <v>37</v>
+      </c>
+      <c r="K81" s="9">
+        <f t="shared" ref="K81:K94" si="53">(G81*$I$5)+(H81*$I$6)+(I81*$I$7)</f>
+        <v>13</v>
+      </c>
+      <c r="L81" s="10">
+        <f t="shared" ref="L81:L94" si="54">J81+K81</f>
+        <v>50</v>
+      </c>
+      <c r="M81" s="11">
+        <f t="shared" ref="M81:M94" si="55">I81*$M$2</f>
+        <v>61.250000000000007</v>
+      </c>
+      <c r="N81" s="11">
+        <f t="shared" ref="N81:N94" si="56">I81*$M$3</f>
+        <v>14.700000000000001</v>
+      </c>
+      <c r="O81" s="9">
+        <v>7</v>
+      </c>
+      <c r="P81" s="9">
+        <v>7</v>
+      </c>
+      <c r="Q81" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="R81" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="S81" s="9"/>
+    </row>
+    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C82" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82" s="12">
         <v>21</v>
       </c>
-      <c r="H81" s="12">
-        <v>0</v>
-      </c>
-      <c r="I81" s="12">
+      <c r="H82" s="12">
+        <v>0</v>
+      </c>
+      <c r="I82" s="12">
         <v>10</v>
       </c>
-      <c r="J81" s="17">
-        <f t="shared" si="47"/>
+      <c r="J82" s="17">
+        <f t="shared" si="52"/>
         <v>42</v>
       </c>
-      <c r="K81" s="9">
-        <f t="shared" si="48"/>
+      <c r="K82" s="9">
+        <f t="shared" si="53"/>
         <v>10.5</v>
       </c>
-      <c r="L81" s="10">
-        <f t="shared" si="49"/>
+      <c r="L82" s="10">
+        <f t="shared" si="54"/>
         <v>52.5</v>
       </c>
-      <c r="M81" s="11">
-        <f t="shared" si="50"/>
+      <c r="M82" s="11">
+        <f t="shared" si="55"/>
         <v>62.5</v>
       </c>
-      <c r="N81" s="11">
-        <f t="shared" si="51"/>
+      <c r="N82" s="11">
+        <f t="shared" si="56"/>
         <v>15</v>
       </c>
-      <c r="O81" s="9">
+      <c r="O82" s="9">
         <v>3</v>
       </c>
-      <c r="P81" s="9">
+      <c r="P82" s="9">
         <v>6</v>
       </c>
-      <c r="Q81" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="R81" s="23"/>
-      <c r="S81" s="9"/>
-      <c r="U81" s="24" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="Q82" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="R82" s="23"/>
+      <c r="S82" s="9"/>
+      <c r="U82" s="24"/>
+    </row>
+    <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
         <v>60</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B83" s="3">
         <v>65</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G82" s="5">
-        <v>20</v>
-      </c>
-      <c r="H82" s="5">
-        <v>10</v>
-      </c>
-      <c r="I82" s="5">
-        <v>10</v>
-      </c>
-      <c r="J82" s="17">
-        <f t="shared" si="47"/>
-        <v>45</v>
-      </c>
-      <c r="K82" s="9">
-        <f t="shared" si="48"/>
-        <v>15</v>
-      </c>
-      <c r="L82" s="10">
-        <f t="shared" si="49"/>
-        <v>60</v>
-      </c>
-      <c r="M82" s="11">
-        <f t="shared" si="50"/>
-        <v>62.5</v>
-      </c>
-      <c r="N82" s="11">
-        <f t="shared" si="51"/>
-        <v>15</v>
-      </c>
-      <c r="O82" s="9">
-        <v>8</v>
-      </c>
-      <c r="P82" s="9">
-        <v>8</v>
-      </c>
-      <c r="Q82" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="R82" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="S82" s="9"/>
-    </row>
-    <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="5" t="s">
         <v>245</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G83" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H83" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I83" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J83" s="17">
-        <f t="shared" si="47"/>
-        <v>50</v>
+        <f t="shared" si="52"/>
+        <v>45</v>
       </c>
       <c r="K83" s="9">
-        <f t="shared" si="48"/>
-        <v>15.5</v>
+        <f t="shared" si="53"/>
+        <v>15</v>
       </c>
       <c r="L83" s="10">
-        <f t="shared" si="49"/>
-        <v>65.5</v>
+        <f t="shared" si="54"/>
+        <v>60</v>
       </c>
       <c r="M83" s="11">
-        <f t="shared" si="50"/>
-        <v>68.75</v>
+        <f t="shared" si="55"/>
+        <v>62.5</v>
       </c>
       <c r="N83" s="11">
-        <f t="shared" si="51"/>
-        <v>16.5</v>
+        <f t="shared" si="56"/>
+        <v>15</v>
       </c>
       <c r="O83" s="9">
         <v>8</v>
@@ -6445,11 +6493,11 @@
       <c r="P83" s="9">
         <v>8</v>
       </c>
-      <c r="Q83" s="23" t="s">
-        <v>306</v>
+      <c r="Q83" s="9" t="s">
+        <v>248</v>
       </c>
       <c r="R83" s="9" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="S83" s="9"/>
     </row>
@@ -6458,42 +6506,42 @@
         <v>245</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G84" s="5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H84" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I84" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J84" s="17">
-        <f t="shared" si="47"/>
-        <v>43</v>
+        <f t="shared" si="52"/>
+        <v>50</v>
       </c>
       <c r="K84" s="9">
-        <f t="shared" si="48"/>
-        <v>17.5</v>
+        <f t="shared" si="53"/>
+        <v>15.5</v>
       </c>
       <c r="L84" s="10">
-        <f t="shared" si="49"/>
-        <v>60.5</v>
+        <f t="shared" si="54"/>
+        <v>65.5</v>
       </c>
       <c r="M84" s="11">
-        <f t="shared" si="50"/>
-        <v>62.5</v>
+        <f t="shared" si="55"/>
+        <v>68.75</v>
       </c>
       <c r="N84" s="11">
-        <f t="shared" si="51"/>
-        <v>15</v>
+        <f t="shared" si="56"/>
+        <v>16.5</v>
       </c>
       <c r="O84" s="9">
         <v>8</v>
@@ -6502,698 +6550,692 @@
         <v>8</v>
       </c>
       <c r="Q84" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="R84" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
+      </c>
+      <c r="R84" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="S84" s="9"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="25" t="s">
-        <v>333</v>
+      <c r="C85" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="F85" s="25" t="s">
-        <v>329</v>
+        <v>252</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="G85" s="5">
+        <v>17</v>
+      </c>
+      <c r="H85" s="5">
+        <v>18</v>
+      </c>
+      <c r="I85" s="5">
+        <v>10</v>
+      </c>
+      <c r="J85" s="17">
+        <f t="shared" si="52"/>
+        <v>43</v>
+      </c>
+      <c r="K85" s="9">
+        <f t="shared" si="53"/>
+        <v>17.5</v>
+      </c>
+      <c r="L85" s="10">
+        <f t="shared" si="54"/>
+        <v>60.5</v>
+      </c>
+      <c r="M85" s="11">
+        <f t="shared" si="55"/>
+        <v>62.5</v>
+      </c>
+      <c r="N85" s="11">
+        <f t="shared" si="56"/>
         <v>15</v>
       </c>
-      <c r="H85" s="5">
-        <v>20</v>
-      </c>
-      <c r="I85" s="5">
-        <v>9</v>
-      </c>
-      <c r="J85" s="17">
-        <f t="shared" si="47"/>
-        <v>40</v>
-      </c>
-      <c r="K85" s="9">
-        <f t="shared" si="48"/>
-        <v>17.5</v>
-      </c>
-      <c r="L85" s="10">
-        <f t="shared" si="49"/>
-        <v>57.5</v>
-      </c>
-      <c r="M85" s="11">
-        <f t="shared" si="50"/>
-        <v>56.25</v>
-      </c>
-      <c r="N85" s="11">
-        <f t="shared" si="51"/>
-        <v>13.5</v>
-      </c>
       <c r="O85" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P85" s="9">
         <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="S85" s="9"/>
-      <c r="U85" s="24"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="D86" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="E86" s="25" t="s">
-        <v>355</v>
-      </c>
-      <c r="F86" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="G86" s="5">
+        <v>15</v>
+      </c>
+      <c r="H86" s="5">
+        <v>20</v>
+      </c>
+      <c r="I86" s="5">
+        <v>9</v>
+      </c>
+      <c r="J86" s="17">
+        <f t="shared" si="52"/>
+        <v>40</v>
+      </c>
+      <c r="K86" s="9">
+        <f t="shared" si="53"/>
+        <v>17.5</v>
+      </c>
+      <c r="L86" s="10">
+        <f t="shared" si="54"/>
+        <v>57.5</v>
+      </c>
+      <c r="M86" s="11">
+        <f t="shared" si="55"/>
+        <v>56.25</v>
+      </c>
+      <c r="N86" s="11">
+        <f t="shared" si="56"/>
+        <v>13.5</v>
+      </c>
+      <c r="O86" s="9">
+        <v>6</v>
+      </c>
+      <c r="P86" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q86" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="R86" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="S86" s="9"/>
+      <c r="U86" s="24"/>
+    </row>
+    <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E87" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G86" s="5">
+      <c r="G87" s="5">
         <v>10</v>
       </c>
-      <c r="H86" s="5">
+      <c r="H87" s="5">
         <v>1</v>
       </c>
-      <c r="I86" s="5">
+      <c r="I87" s="5">
         <v>10</v>
       </c>
-      <c r="J86" s="17">
-        <f t="shared" si="47"/>
+      <c r="J87" s="17">
+        <f t="shared" si="52"/>
         <v>20.5</v>
       </c>
-      <c r="K86" s="9">
-        <f t="shared" si="48"/>
+      <c r="K87" s="9">
+        <f t="shared" si="53"/>
         <v>5.5</v>
       </c>
-      <c r="L86" s="10">
-        <f t="shared" si="49"/>
+      <c r="L87" s="10">
+        <f t="shared" si="54"/>
         <v>26</v>
       </c>
-      <c r="M86" s="11">
-        <f t="shared" si="50"/>
+      <c r="M87" s="11">
+        <f t="shared" si="55"/>
         <v>62.5</v>
       </c>
-      <c r="N86" s="11">
-        <f t="shared" si="51"/>
+      <c r="N87" s="11">
+        <f t="shared" si="56"/>
         <v>15</v>
       </c>
-      <c r="O86" s="9">
+      <c r="O87" s="9">
         <v>4</v>
       </c>
-      <c r="P86" s="9">
+      <c r="P87" s="9">
         <v>6</v>
       </c>
-      <c r="Q86" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="R86" s="23"/>
-      <c r="S86" s="9"/>
-      <c r="U86" s="24" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="Q87" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="R87" s="23"/>
+      <c r="S87" s="9"/>
+      <c r="U87" s="24"/>
+    </row>
+    <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
         <v>70</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B88" s="3">
         <v>70</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G87" s="12">
-        <v>25</v>
-      </c>
-      <c r="H87" s="12">
-        <v>8</v>
-      </c>
-      <c r="I87" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="J87" s="17">
-        <f t="shared" si="47"/>
-        <v>54</v>
-      </c>
-      <c r="K87" s="9">
-        <f t="shared" si="48"/>
-        <v>16.5</v>
-      </c>
-      <c r="L87" s="10">
-        <f t="shared" si="49"/>
-        <v>70.5</v>
-      </c>
-      <c r="M87" s="11">
-        <f t="shared" si="50"/>
-        <v>72.5</v>
-      </c>
-      <c r="N87" s="11">
-        <f t="shared" si="51"/>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="O87" s="9">
-        <v>7</v>
-      </c>
-      <c r="P87" s="9">
-        <v>9</v>
-      </c>
-      <c r="Q87" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="R87" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="S87" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12" t="s">
         <v>254</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G88" s="12">
+        <v>25</v>
+      </c>
+      <c r="H88" s="12">
+        <v>8</v>
+      </c>
+      <c r="I88" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="J88" s="17">
+        <f t="shared" si="52"/>
+        <v>54</v>
+      </c>
+      <c r="K88" s="9">
+        <f t="shared" si="53"/>
+        <v>16.5</v>
+      </c>
+      <c r="L88" s="10">
+        <f t="shared" si="54"/>
+        <v>70.5</v>
+      </c>
+      <c r="M88" s="11">
+        <f t="shared" si="55"/>
+        <v>72.5</v>
+      </c>
+      <c r="N88" s="11">
+        <f t="shared" si="56"/>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="O88" s="9">
+        <v>7</v>
+      </c>
+      <c r="P88" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q88" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="R88" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="S88" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G89" s="12">
         <v>20</v>
       </c>
-      <c r="H88" s="12">
+      <c r="H89" s="12">
         <v>23</v>
-      </c>
-      <c r="I88" s="12">
-        <v>11</v>
-      </c>
-      <c r="J88" s="17">
-        <f t="shared" si="47"/>
-        <v>51.5</v>
-      </c>
-      <c r="K88" s="9">
-        <f t="shared" si="48"/>
-        <v>21.5</v>
-      </c>
-      <c r="L88" s="10">
-        <f t="shared" si="49"/>
-        <v>73</v>
-      </c>
-      <c r="M88" s="11">
-        <f t="shared" si="50"/>
-        <v>68.75</v>
-      </c>
-      <c r="N88" s="11">
-        <f t="shared" si="51"/>
-        <v>16.5</v>
-      </c>
-      <c r="O88" s="9">
-        <v>6</v>
-      </c>
-      <c r="P88" s="9">
-        <v>6</v>
-      </c>
-      <c r="Q88" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="R88" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="S88" s="23" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="E89" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="G89" s="12">
-        <v>14</v>
-      </c>
-      <c r="H89" s="12">
-        <v>37</v>
       </c>
       <c r="I89" s="12">
         <v>11</v>
       </c>
       <c r="J89" s="17">
-        <f t="shared" ref="J89" si="52">(G89*$I$2)+(H89*$I$3)</f>
-        <v>46.5</v>
+        <f t="shared" si="52"/>
+        <v>51.5</v>
       </c>
       <c r="K89" s="9">
-        <f t="shared" ref="K89" si="53">(G89*$I$5)+(H89*$I$6)+(I89*$I$7)</f>
-        <v>25.5</v>
+        <f t="shared" si="53"/>
+        <v>21.5</v>
       </c>
       <c r="L89" s="10">
-        <f t="shared" ref="L89" si="54">J89+K89</f>
-        <v>72</v>
+        <f t="shared" si="54"/>
+        <v>73</v>
       </c>
       <c r="M89" s="11">
-        <f t="shared" ref="M89" si="55">I89*$M$2</f>
+        <f t="shared" si="55"/>
         <v>68.75</v>
       </c>
       <c r="N89" s="11">
-        <f t="shared" ref="N89" si="56">I89*$M$3</f>
+        <f t="shared" si="56"/>
         <v>16.5</v>
       </c>
       <c r="O89" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P89" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q89" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="R89" s="23"/>
-      <c r="S89" s="23"/>
-      <c r="U89" s="24" t="s">
-        <v>330</v>
+        <v>311</v>
+      </c>
+      <c r="R89" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="S89" s="23" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F90" s="26" t="s">
         <v>329</v>
       </c>
       <c r="G90" s="12">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H90" s="12">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I90" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J90" s="17">
-        <f t="shared" si="47"/>
-        <v>52</v>
+        <f t="shared" ref="J90" si="57">(G90*$I$2)+(H90*$I$3)</f>
+        <v>46.5</v>
       </c>
       <c r="K90" s="9">
-        <f t="shared" si="48"/>
-        <v>20.5</v>
+        <f t="shared" ref="K90" si="58">(G90*$I$5)+(H90*$I$6)+(I90*$I$7)</f>
+        <v>25.5</v>
       </c>
       <c r="L90" s="10">
-        <f t="shared" si="49"/>
-        <v>72.5</v>
+        <f t="shared" ref="L90" si="59">J90+K90</f>
+        <v>72</v>
       </c>
       <c r="M90" s="11">
-        <f t="shared" si="50"/>
-        <v>62.5</v>
+        <f t="shared" ref="M90" si="60">I90*$M$2</f>
+        <v>68.75</v>
       </c>
       <c r="N90" s="11">
-        <f t="shared" si="51"/>
-        <v>15</v>
+        <f t="shared" ref="N90" si="61">I90*$M$3</f>
+        <v>16.5</v>
       </c>
       <c r="O90" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P90" s="9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q90" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="R90" s="23" t="s">
-        <v>342</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="R90" s="23"/>
       <c r="S90" s="23"/>
       <c r="U90" s="24"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="C91" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="F91" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="G91" s="12">
+        <v>21</v>
+      </c>
+      <c r="H91" s="12">
+        <v>20</v>
+      </c>
+      <c r="I91" s="12">
+        <v>10</v>
+      </c>
+      <c r="J91" s="17">
+        <f t="shared" si="52"/>
+        <v>52</v>
+      </c>
+      <c r="K91" s="9">
+        <f t="shared" si="53"/>
+        <v>20.5</v>
+      </c>
+      <c r="L91" s="10">
+        <f t="shared" si="54"/>
+        <v>72.5</v>
+      </c>
+      <c r="M91" s="11">
+        <f t="shared" si="55"/>
+        <v>62.5</v>
+      </c>
+      <c r="N91" s="11">
+        <f t="shared" si="56"/>
+        <v>15</v>
+      </c>
+      <c r="O91" s="9">
+        <v>6</v>
+      </c>
+      <c r="P91" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="R91" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="S91" s="23"/>
+      <c r="U91" s="24"/>
+    </row>
+    <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
         <v>80</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B92" s="3">
         <v>75</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D91" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G91" s="5">
-        <v>27</v>
-      </c>
-      <c r="H91" s="5">
-        <v>14</v>
-      </c>
-      <c r="I91" s="5">
-        <v>12</v>
-      </c>
-      <c r="J91" s="17">
-        <f t="shared" si="47"/>
-        <v>61</v>
-      </c>
-      <c r="K91" s="9">
-        <f t="shared" si="48"/>
-        <v>20.5</v>
-      </c>
-      <c r="L91" s="10">
-        <f t="shared" si="49"/>
-        <v>81.5</v>
-      </c>
-      <c r="M91" s="11">
-        <f t="shared" si="50"/>
-        <v>75</v>
-      </c>
-      <c r="N91" s="11">
-        <f t="shared" si="51"/>
-        <v>18</v>
-      </c>
-      <c r="O91" s="9">
-        <v>8</v>
-      </c>
-      <c r="P91" s="9">
-        <v>9</v>
-      </c>
-      <c r="Q91" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="R91" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="S91" s="23" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C92" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>263</v>
+      <c r="D92" s="22" t="s">
+        <v>260</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G92" s="5">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H92" s="5">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I92" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J92" s="17">
-        <f t="shared" si="47"/>
-        <v>36</v>
+        <f t="shared" si="52"/>
+        <v>61</v>
       </c>
       <c r="K92" s="9">
-        <f t="shared" si="48"/>
-        <v>19.5</v>
+        <f t="shared" si="53"/>
+        <v>20.5</v>
       </c>
       <c r="L92" s="10">
-        <f t="shared" si="49"/>
-        <v>55.5</v>
+        <f t="shared" si="54"/>
+        <v>81.5</v>
       </c>
       <c r="M92" s="11">
-        <f t="shared" si="50"/>
-        <v>62.5</v>
+        <f t="shared" si="55"/>
+        <v>75</v>
       </c>
       <c r="N92" s="11">
-        <f t="shared" si="51"/>
-        <v>15</v>
+        <f t="shared" si="56"/>
+        <v>18</v>
       </c>
       <c r="O92" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P92" s="9">
-        <v>6</v>
-      </c>
-      <c r="Q92" s="23" t="s">
-        <v>325</v>
+        <v>9</v>
+      </c>
+      <c r="Q92" s="9" t="s">
+        <v>262</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="S92" s="9"/>
+        <v>315</v>
+      </c>
+      <c r="S92" s="23" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="5" t="s">
         <v>259</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G93" s="5">
+        <v>11</v>
+      </c>
+      <c r="H93" s="5">
+        <v>28</v>
+      </c>
+      <c r="I93" s="5">
         <v>10</v>
       </c>
-      <c r="H93" s="5">
-        <v>35</v>
-      </c>
-      <c r="I93" s="5">
-        <v>10.5</v>
-      </c>
       <c r="J93" s="17">
-        <f t="shared" si="47"/>
-        <v>37.5</v>
+        <f t="shared" si="52"/>
+        <v>36</v>
       </c>
       <c r="K93" s="9">
-        <f t="shared" si="48"/>
-        <v>22.5</v>
+        <f t="shared" si="53"/>
+        <v>19.5</v>
       </c>
       <c r="L93" s="10">
-        <f t="shared" si="49"/>
-        <v>60</v>
+        <f t="shared" si="54"/>
+        <v>55.5</v>
       </c>
       <c r="M93" s="11">
-        <f t="shared" si="50"/>
-        <v>65.625</v>
+        <f t="shared" si="55"/>
+        <v>62.5</v>
       </c>
       <c r="N93" s="11">
-        <f t="shared" si="51"/>
-        <v>15.75</v>
+        <f t="shared" si="56"/>
+        <v>15</v>
       </c>
       <c r="O93" s="9">
         <v>6</v>
       </c>
       <c r="P93" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q93" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="R93" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="S93" s="23" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C94" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G94" s="5">
+        <v>10</v>
+      </c>
+      <c r="H94" s="5">
+        <v>35</v>
+      </c>
+      <c r="I94" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="J94" s="17">
+        <f t="shared" si="52"/>
+        <v>37.5</v>
+      </c>
+      <c r="K94" s="9">
+        <f t="shared" si="53"/>
+        <v>22.5</v>
+      </c>
+      <c r="L94" s="10">
+        <f t="shared" si="54"/>
+        <v>60</v>
+      </c>
+      <c r="M94" s="11">
+        <f t="shared" si="55"/>
+        <v>65.625</v>
+      </c>
+      <c r="N94" s="11">
+        <f t="shared" si="56"/>
+        <v>15.75</v>
+      </c>
+      <c r="O94" s="9">
+        <v>6</v>
+      </c>
+      <c r="P94" s="9">
         <v>8</v>
       </c>
-      <c r="Q93" s="23" t="s">
+      <c r="Q94" s="23" t="s">
         <v>318</v>
-      </c>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-    </row>
-    <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>60</v>
-      </c>
-      <c r="B94" s="3">
-        <v>65</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G94" s="12">
-        <v>12</v>
-      </c>
-      <c r="H94" s="12">
-        <v>30</v>
-      </c>
-      <c r="I94" s="12">
-        <v>10.5</v>
-      </c>
-      <c r="J94" s="17">
-        <f t="shared" ref="J94:J104" si="57">(G94*$I$2)+(H94*$I$3)</f>
-        <v>39</v>
-      </c>
-      <c r="K94" s="9">
-        <f t="shared" ref="K94:K116" si="58">(G94*$I$5)+(H94*$I$6)+(I94*$I$7)</f>
-        <v>21</v>
-      </c>
-      <c r="L94" s="10">
-        <f t="shared" ref="L94:L104" si="59">J94+K94</f>
-        <v>60</v>
-      </c>
-      <c r="M94" s="11">
-        <f t="shared" ref="M94:M117" si="60">I94*$M$2</f>
-        <v>65.625</v>
-      </c>
-      <c r="N94" s="11">
-        <f t="shared" ref="N94:N117" si="61">I94*$M$3</f>
-        <v>15.75</v>
-      </c>
-      <c r="O94" s="9">
-        <v>9</v>
-      </c>
-      <c r="P94" s="9">
-        <v>9</v>
-      </c>
-      <c r="Q94" s="23" t="s">
-        <v>319</v>
       </c>
       <c r="R94" s="9"/>
       <c r="S94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="3">
+        <v>60</v>
+      </c>
+      <c r="B95" s="3">
+        <v>65</v>
+      </c>
       <c r="C95" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D95" s="21" t="s">
-        <v>270</v>
+      <c r="D95" s="12" t="s">
+        <v>268</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G95" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H95" s="12">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I95" s="12">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="J95" s="17">
-        <f t="shared" si="57"/>
-        <v>27.5</v>
+        <f t="shared" ref="J95:J105" si="62">(G95*$I$2)+(H95*$I$3)</f>
+        <v>39</v>
       </c>
       <c r="K95" s="9">
-        <f t="shared" si="58"/>
-        <v>12.5</v>
+        <f t="shared" ref="K95:K117" si="63">(G95*$I$5)+(H95*$I$6)+(I95*$I$7)</f>
+        <v>21</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" si="59"/>
-        <v>40</v>
+        <f t="shared" ref="L95:L105" si="64">J95+K95</f>
+        <v>60</v>
       </c>
       <c r="M95" s="11">
-        <f t="shared" si="60"/>
-        <v>43.75</v>
+        <f t="shared" ref="M95:M118" si="65">I95*$M$2</f>
+        <v>65.625</v>
       </c>
       <c r="N95" s="11">
-        <f t="shared" si="61"/>
-        <v>10.5</v>
+        <f t="shared" ref="N95:N118" si="66">I95*$M$3</f>
+        <v>15.75</v>
       </c>
       <c r="O95" s="9">
         <v>9</v>
       </c>
       <c r="P95" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q95" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R95" s="9"/>
       <c r="S95" s="9"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>75</v>
-      </c>
-      <c r="B96" s="3">
-        <v>80</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F96" s="5" t="s">
+      <c r="C96" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F96" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G96" s="5">
-        <v>25</v>
-      </c>
-      <c r="H96" s="5">
-        <v>13</v>
-      </c>
-      <c r="I96" s="5">
-        <v>12.7</v>
+      <c r="G96" s="12">
+        <v>10</v>
+      </c>
+      <c r="H96" s="12">
+        <v>15</v>
+      </c>
+      <c r="I96" s="12">
+        <v>7</v>
       </c>
       <c r="J96" s="17">
-        <f t="shared" si="57"/>
-        <v>56.5</v>
+        <f t="shared" si="62"/>
+        <v>27.5</v>
       </c>
       <c r="K96" s="9">
-        <f t="shared" si="58"/>
-        <v>19</v>
+        <f t="shared" si="63"/>
+        <v>12.5</v>
       </c>
       <c r="L96" s="10">
-        <f t="shared" si="59"/>
-        <v>75.5</v>
+        <f t="shared" si="64"/>
+        <v>40</v>
       </c>
       <c r="M96" s="11">
-        <f t="shared" si="60"/>
-        <v>79.375</v>
+        <f t="shared" si="65"/>
+        <v>43.75</v>
       </c>
       <c r="N96" s="11">
-        <f t="shared" si="61"/>
-        <v>19.049999999999997</v>
+        <f t="shared" si="66"/>
+        <v>10.5</v>
       </c>
       <c r="O96" s="9">
         <v>9</v>
@@ -7201,25 +7243,27 @@
       <c r="P96" s="9">
         <v>10</v>
       </c>
-      <c r="Q96" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="R96" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="S96" s="9" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q96" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="R96" s="9"/>
+      <c r="S96" s="9"/>
+    </row>
+    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>75</v>
+      </c>
+      <c r="B97" s="3">
+        <v>80</v>
+      </c>
       <c r="C97" s="5" t="s">
         <v>272</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>57</v>
@@ -7228,91 +7272,118 @@
         <v>25</v>
       </c>
       <c r="H97" s="5">
+        <v>13</v>
+      </c>
+      <c r="I97" s="5">
+        <v>12.7</v>
+      </c>
+      <c r="J97" s="17">
+        <f t="shared" si="62"/>
+        <v>56.5</v>
+      </c>
+      <c r="K97" s="9">
+        <f t="shared" si="63"/>
+        <v>19</v>
+      </c>
+      <c r="L97" s="10">
+        <f t="shared" si="64"/>
+        <v>75.5</v>
+      </c>
+      <c r="M97" s="11">
+        <f t="shared" si="65"/>
+        <v>79.375</v>
+      </c>
+      <c r="N97" s="11">
+        <f t="shared" si="66"/>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="O97" s="9">
+        <v>9</v>
+      </c>
+      <c r="P97" s="9">
         <v>10</v>
       </c>
-      <c r="I97" s="5">
+      <c r="Q97" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="R97" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="S97" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="T97" s="24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C98" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G98" s="5">
+        <v>25</v>
+      </c>
+      <c r="H98" s="5">
+        <v>10</v>
+      </c>
+      <c r="I98" s="5">
         <v>12</v>
       </c>
-      <c r="J97" s="17">
-        <f t="shared" si="57"/>
+      <c r="J98" s="17">
+        <f t="shared" si="62"/>
         <v>55</v>
       </c>
-      <c r="K97" s="9">
-        <f t="shared" si="58"/>
+      <c r="K98" s="9">
+        <f t="shared" si="63"/>
         <v>17.5</v>
       </c>
-      <c r="L97" s="10">
-        <f t="shared" si="59"/>
+      <c r="L98" s="10">
+        <f t="shared" si="64"/>
         <v>72.5</v>
       </c>
-      <c r="M97" s="11">
-        <f t="shared" si="60"/>
+      <c r="M98" s="11">
+        <f t="shared" si="65"/>
         <v>75</v>
       </c>
-      <c r="N97" s="11">
-        <f t="shared" si="61"/>
+      <c r="N98" s="11">
+        <f t="shared" si="66"/>
         <v>18</v>
       </c>
-      <c r="O97" s="9">
+      <c r="O98" s="9">
         <v>8</v>
       </c>
-      <c r="P97" s="9">
+      <c r="P98" s="9">
         <v>12</v>
       </c>
-      <c r="Q97" s="9" t="s">
+      <c r="Q98" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="R97" s="23" t="s">
+      <c r="R98" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="S97" s="23" t="s">
+      <c r="S98" s="23" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3">
         <v>77</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B99" s="3">
         <v>85</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C99" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="17">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="K98" s="9">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="L98" s="10">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="11">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="N98" s="11">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="O98" s="9"/>
-      <c r="P98" s="9"/>
-      <c r="Q98" s="9"/>
-      <c r="R98" s="9"/>
-      <c r="S98" s="9"/>
-    </row>
-    <row r="99" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
@@ -7320,23 +7391,23 @@
       <c r="H99" s="9"/>
       <c r="I99" s="9"/>
       <c r="J99" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K99" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M99" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N99" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O99" s="9"/>
@@ -7345,16 +7416,8 @@
       <c r="R99" s="9"/>
       <c r="S99" s="9"/>
     </row>
-    <row r="100" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
-        <v>80</v>
-      </c>
-      <c r="B100" s="3">
-        <v>90</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>280</v>
-      </c>
+    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
@@ -7362,23 +7425,23 @@
       <c r="H100" s="9"/>
       <c r="I100" s="9"/>
       <c r="J100" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K100" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M100" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N100" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O100" s="9"/>
@@ -7387,8 +7450,16 @@
       <c r="R100" s="9"/>
       <c r="S100" s="9"/>
     </row>
-    <row r="101" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="9"/>
+    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="3">
+        <v>80</v>
+      </c>
+      <c r="B101" s="3">
+        <v>90</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>280</v>
+      </c>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
@@ -7396,23 +7467,23 @@
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
       <c r="J101" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K101" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L101" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M101" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N101" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O101" s="9"/>
@@ -7421,7 +7492,7 @@
       <c r="R101" s="9"/>
       <c r="S101" s="9"/>
     </row>
-    <row r="102" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -7430,23 +7501,23 @@
       <c r="H102" s="9"/>
       <c r="I102" s="9"/>
       <c r="J102" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K102" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L102" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M102" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N102" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O102" s="9"/>
@@ -7455,7 +7526,7 @@
       <c r="R102" s="9"/>
       <c r="S102" s="9"/>
     </row>
-    <row r="103" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -7464,23 +7535,23 @@
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K103" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L103" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M103" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N103" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O103" s="9"/>
@@ -7489,7 +7560,7 @@
       <c r="R103" s="9"/>
       <c r="S103" s="9"/>
     </row>
-    <row r="104" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -7498,23 +7569,23 @@
       <c r="H104" s="9"/>
       <c r="I104" s="9"/>
       <c r="J104" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K104" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L104" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M104" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N104" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O104" s="9"/>
@@ -7523,7 +7594,7 @@
       <c r="R104" s="9"/>
       <c r="S104" s="9"/>
     </row>
-    <row r="105" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -7532,23 +7603,23 @@
       <c r="H105" s="9"/>
       <c r="I105" s="9"/>
       <c r="J105" s="17">
-        <f t="shared" ref="J105:J125" si="62">(G105*$I$2)+(H105*$I$3)</f>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K105" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L105" s="10">
-        <f t="shared" ref="L105:L125" si="63">J105+K105</f>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M105" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N105" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O105" s="9"/>
@@ -7557,7 +7628,7 @@
       <c r="R105" s="9"/>
       <c r="S105" s="9"/>
     </row>
-    <row r="106" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -7566,23 +7637,23 @@
       <c r="H106" s="9"/>
       <c r="I106" s="9"/>
       <c r="J106" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="J106:J126" si="67">(G106*$I$2)+(H106*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K106" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L106" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="L106:L126" si="68">J106+K106</f>
         <v>0</v>
       </c>
       <c r="M106" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N106" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O106" s="9"/>
@@ -7591,7 +7662,7 @@
       <c r="R106" s="9"/>
       <c r="S106" s="9"/>
     </row>
-    <row r="107" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -7600,23 +7671,23 @@
       <c r="H107" s="9"/>
       <c r="I107" s="9"/>
       <c r="J107" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K107" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L107" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M107" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N107" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O107" s="9"/>
@@ -7625,7 +7696,7 @@
       <c r="R107" s="9"/>
       <c r="S107" s="9"/>
     </row>
-    <row r="108" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -7634,23 +7705,23 @@
       <c r="H108" s="9"/>
       <c r="I108" s="9"/>
       <c r="J108" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K108" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L108" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M108" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N108" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O108" s="9"/>
@@ -7659,7 +7730,7 @@
       <c r="R108" s="9"/>
       <c r="S108" s="9"/>
     </row>
-    <row r="109" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -7668,23 +7739,23 @@
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K109" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L109" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M109" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N109" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O109" s="9"/>
@@ -7693,7 +7764,7 @@
       <c r="R109" s="9"/>
       <c r="S109" s="9"/>
     </row>
-    <row r="110" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -7702,23 +7773,23 @@
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
       <c r="J110" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K110" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L110" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M110" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N110" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O110" s="9"/>
@@ -7727,7 +7798,7 @@
       <c r="R110" s="9"/>
       <c r="S110" s="9"/>
     </row>
-    <row r="111" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -7736,23 +7807,23 @@
       <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K111" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L111" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M111" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N111" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O111" s="9"/>
@@ -7761,7 +7832,7 @@
       <c r="R111" s="9"/>
       <c r="S111" s="9"/>
     </row>
-    <row r="112" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -7770,23 +7841,23 @@
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
       <c r="J112" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K112" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L112" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M112" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N112" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O112" s="9"/>
@@ -7804,23 +7875,23 @@
       <c r="H113" s="9"/>
       <c r="I113" s="9"/>
       <c r="J113" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K113" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L113" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M113" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N113" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O113" s="9"/>
@@ -7838,23 +7909,23 @@
       <c r="H114" s="9"/>
       <c r="I114" s="9"/>
       <c r="J114" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K114" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L114" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M114" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N114" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O114" s="9"/>
@@ -7872,23 +7943,23 @@
       <c r="H115" s="9"/>
       <c r="I115" s="9"/>
       <c r="J115" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K115" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L115" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M115" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N115" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O115" s="9"/>
@@ -7906,23 +7977,23 @@
       <c r="H116" s="9"/>
       <c r="I116" s="9"/>
       <c r="J116" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K116" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L116" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M116" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N116" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O116" s="9"/>
@@ -7940,23 +8011,23 @@
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K117" s="9">
-        <f t="shared" ref="K117:K161" si="64">(G117*$I$5)+(H117*$I$6)+(I117*$I$7)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L117" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M117" s="11">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N117" s="11">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O117" s="9"/>
@@ -7974,23 +8045,23 @@
       <c r="H118" s="9"/>
       <c r="I118" s="9"/>
       <c r="J118" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K118" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" ref="K118:K162" si="69">(G118*$I$5)+(H118*$I$6)+(I118*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L118" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M118" s="11">
-        <f t="shared" ref="M118:M161" si="65">I118*$M$2</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N118" s="11">
-        <f t="shared" ref="N118:N161" si="66">I118*$M$3</f>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O118" s="9"/>
@@ -8008,23 +8079,23 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K119" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L119" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M119" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" ref="M119:M162" si="70">I119*$M$2</f>
         <v>0</v>
       </c>
       <c r="N119" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" ref="N119:N162" si="71">I119*$M$3</f>
         <v>0</v>
       </c>
       <c r="O119" s="9"/>
@@ -8042,23 +8113,23 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
       <c r="J120" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K120" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L120" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M120" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N120" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O120" s="9"/>
@@ -8076,23 +8147,23 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K121" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M121" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N121" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O121" s="9"/>
@@ -8110,23 +8181,23 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
       <c r="J122" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K122" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M122" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N122" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O122" s="9"/>
@@ -8144,23 +8215,23 @@
       <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K123" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L123" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M123" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N123" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O123" s="9"/>
@@ -8178,23 +8249,23 @@
       <c r="H124" s="9"/>
       <c r="I124" s="9"/>
       <c r="J124" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K124" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L124" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M124" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N124" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O124" s="9"/>
@@ -8212,23 +8283,23 @@
       <c r="H125" s="9"/>
       <c r="I125" s="9"/>
       <c r="J125" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K125" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L125" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M125" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N125" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O125" s="9"/>
@@ -8246,23 +8317,23 @@
       <c r="H126" s="9"/>
       <c r="I126" s="9"/>
       <c r="J126" s="17">
-        <f t="shared" ref="J126:J161" si="67">(G126*$I$2)+(H126*$I$3)</f>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K126" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L126" s="10">
-        <f t="shared" ref="L126:L161" si="68">J126+K126</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M126" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N126" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O126" s="9"/>
@@ -8280,23 +8351,23 @@
       <c r="H127" s="9"/>
       <c r="I127" s="9"/>
       <c r="J127" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" ref="J127:J162" si="72">(G127*$I$2)+(H127*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K127" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L127" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" ref="L127:L162" si="73">J127+K127</f>
         <v>0</v>
       </c>
       <c r="M127" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N127" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O127" s="9"/>
@@ -8314,23 +8385,23 @@
       <c r="H128" s="9"/>
       <c r="I128" s="9"/>
       <c r="J128" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K128" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L128" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M128" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N128" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O128" s="9"/>
@@ -8348,23 +8419,23 @@
       <c r="H129" s="9"/>
       <c r="I129" s="9"/>
       <c r="J129" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K129" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L129" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M129" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N129" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O129" s="9"/>
@@ -8382,23 +8453,23 @@
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
       <c r="J130" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K130" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L130" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M130" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N130" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O130" s="9"/>
@@ -8416,23 +8487,23 @@
       <c r="H131" s="9"/>
       <c r="I131" s="9"/>
       <c r="J131" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K131" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M131" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N131" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O131" s="9"/>
@@ -8450,23 +8521,23 @@
       <c r="H132" s="9"/>
       <c r="I132" s="9"/>
       <c r="J132" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K132" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L132" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M132" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N132" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O132" s="9"/>
@@ -8484,23 +8555,23 @@
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
       <c r="J133" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K133" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M133" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N133" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O133" s="9"/>
@@ -8518,23 +8589,23 @@
       <c r="H134" s="9"/>
       <c r="I134" s="9"/>
       <c r="J134" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K134" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L134" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M134" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N134" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O134" s="9"/>
@@ -8552,23 +8623,23 @@
       <c r="H135" s="9"/>
       <c r="I135" s="9"/>
       <c r="J135" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K135" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L135" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M135" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N135" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O135" s="9"/>
@@ -8586,23 +8657,23 @@
       <c r="H136" s="9"/>
       <c r="I136" s="9"/>
       <c r="J136" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K136" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L136" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M136" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N136" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O136" s="9"/>
@@ -8620,23 +8691,23 @@
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K137" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L137" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M137" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N137" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O137" s="9"/>
@@ -8654,23 +8725,23 @@
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
       <c r="J138" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K138" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L138" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M138" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N138" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O138" s="9"/>
@@ -8688,23 +8759,23 @@
       <c r="H139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K139" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L139" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M139" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N139" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O139" s="9"/>
@@ -8722,23 +8793,23 @@
       <c r="H140" s="9"/>
       <c r="I140" s="9"/>
       <c r="J140" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K140" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L140" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M140" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N140" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O140" s="9"/>
@@ -8756,23 +8827,23 @@
       <c r="H141" s="9"/>
       <c r="I141" s="9"/>
       <c r="J141" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K141" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L141" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M141" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N141" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O141" s="9"/>
@@ -8790,23 +8861,23 @@
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
       <c r="J142" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K142" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L142" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M142" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N142" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O142" s="9"/>
@@ -8824,23 +8895,23 @@
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K143" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L143" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M143" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N143" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O143" s="9"/>
@@ -8858,23 +8929,23 @@
       <c r="H144" s="9"/>
       <c r="I144" s="9"/>
       <c r="J144" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K144" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L144" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M144" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N144" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O144" s="9"/>
@@ -8892,23 +8963,23 @@
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
       <c r="J145" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K145" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L145" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M145" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N145" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O145" s="9"/>
@@ -8926,23 +8997,23 @@
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
       <c r="J146" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K146" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L146" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M146" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N146" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O146" s="9"/>
@@ -8960,23 +9031,23 @@
       <c r="H147" s="9"/>
       <c r="I147" s="9"/>
       <c r="J147" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K147" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L147" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M147" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N147" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O147" s="9"/>
@@ -8994,23 +9065,23 @@
       <c r="H148" s="9"/>
       <c r="I148" s="9"/>
       <c r="J148" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K148" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L148" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M148" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N148" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O148" s="9"/>
@@ -9028,23 +9099,23 @@
       <c r="H149" s="9"/>
       <c r="I149" s="9"/>
       <c r="J149" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K149" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L149" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M149" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N149" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O149" s="9"/>
@@ -9062,23 +9133,23 @@
       <c r="H150" s="9"/>
       <c r="I150" s="9"/>
       <c r="J150" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K150" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L150" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M150" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N150" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O150" s="9"/>
@@ -9096,23 +9167,23 @@
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K151" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L151" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M151" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N151" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O151" s="9"/>
@@ -9130,23 +9201,23 @@
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
       <c r="J152" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K152" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L152" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M152" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N152" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O152" s="9"/>
@@ -9164,23 +9235,23 @@
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
       <c r="J153" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K153" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L153" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M153" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N153" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O153" s="9"/>
@@ -9198,23 +9269,23 @@
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
       <c r="J154" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K154" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L154" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M154" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N154" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O154" s="9"/>
@@ -9232,23 +9303,23 @@
       <c r="H155" s="9"/>
       <c r="I155" s="9"/>
       <c r="J155" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K155" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L155" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M155" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N155" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O155" s="9"/>
@@ -9266,23 +9337,23 @@
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
       <c r="J156" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K156" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L156" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M156" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N156" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O156" s="9"/>
@@ -9300,23 +9371,23 @@
       <c r="H157" s="9"/>
       <c r="I157" s="9"/>
       <c r="J157" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K157" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L157" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M157" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N157" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O157" s="9"/>
@@ -9334,23 +9405,23 @@
       <c r="H158" s="9"/>
       <c r="I158" s="9"/>
       <c r="J158" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K158" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L158" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M158" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N158" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O158" s="9"/>
@@ -9368,23 +9439,23 @@
       <c r="H159" s="9"/>
       <c r="I159" s="9"/>
       <c r="J159" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K159" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L159" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M159" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N159" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O159" s="9"/>
@@ -9402,23 +9473,23 @@
       <c r="H160" s="9"/>
       <c r="I160" s="9"/>
       <c r="J160" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K160" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L160" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M160" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N160" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O160" s="9"/>
@@ -9436,23 +9507,23 @@
       <c r="H161" s="9"/>
       <c r="I161" s="9"/>
       <c r="J161" s="17">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K161" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="L161" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M161" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="N161" s="11">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="O161" s="9"/>
@@ -9460,6 +9531,40 @@
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
       <c r="S161" s="9"/>
+    </row>
+    <row r="162" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
+      <c r="E162" s="9"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="9"/>
+      <c r="H162" s="9"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="17">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="K162" s="9">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="L162" s="10">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="M162" s="11">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="N162" s="11">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="O162" s="9"/>
+      <c r="P162" s="9"/>
+      <c r="Q162" s="9"/>
+      <c r="R162" s="9"/>
+      <c r="S162" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9516,7 +9621,7 @@
         <v>49</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9542,10 +9647,10 @@
         <v>4</v>
       </c>
       <c r="H2" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>331</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>332</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -9556,10 +9661,10 @@
     </row>
     <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C3" s="5">
         <v>13</v>
@@ -9589,10 +9694,10 @@
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C4" s="5">
         <v>9</v>
@@ -9610,7 +9715,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="9"/>
@@ -9622,10 +9727,10 @@
     </row>
     <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C5" s="12">
         <v>21</v>
@@ -9643,7 +9748,7 @@
         <v>6</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="9"/>
@@ -9655,10 +9760,10 @@
     </row>
     <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C6" s="5">
         <v>10</v>
@@ -9676,7 +9781,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="9"/>
@@ -9688,10 +9793,10 @@
     </row>
     <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C7" s="12">
         <v>14</v>
@@ -9709,7 +9814,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
